--- a/InputData/io-model/BECbIC/BAU Employee Compensation by ISIC Code.xlsx
+++ b/InputData/io-model/BECbIC/BAU Employee Compensation by ISIC Code.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\io-model\BECbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F5283A-EB7B-419A-93F3-951A29FD7E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F4D3B3-F6F0-483B-9CC6-8B9FFD7C5366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2399,12 +2399,6 @@
   </si>
   <si>
     <t xml:space="preserve">Current Employment Statistics </t>
-  </si>
-  <si>
-    <t>We convert 2021 USD to 2012 USD with the following conversion factor:</t>
-  </si>
-  <si>
-    <t>2012 USD per 2021 USD</t>
   </si>
   <si>
     <t>ISIC 351; ISIC 352T353; ISIC 36T39</t>
@@ -3758,6 +3752,12 @@
   <si>
     <t>ISIC 45T47; ISIC 31T33; ISIC 90T96; ISIC 97T98</t>
   </si>
+  <si>
+    <t>2012 USD per 2024 USD</t>
+  </si>
+  <si>
+    <t>We convert 2024 USD to 2012 USD with the following conversion factor:</t>
+  </si>
 </sst>
 </file>
 
@@ -3767,7 +3767,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0_ ;\-#,##0.0\ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000E+00"/>
-    <numFmt numFmtId="173" formatCode="0.000E+00"/>
+    <numFmt numFmtId="167" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -4203,7 +4203,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4353,6 +4353,7 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -4383,8 +4384,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4819,15 +4818,15 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>780</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="16">
-        <v>0.84730412960844359</v>
+        <v>0.73191600598044548</v>
       </c>
       <c r="B36" t="s">
-        <v>781</v>
+        <v>1221</v>
       </c>
     </row>
   </sheetData>
@@ -4872,186 +4871,186 @@
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="80" t="s">
+      <c r="B3" s="75"/>
+      <c r="C3" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="83"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="75" t="s">
+      <c r="B4" s="75"/>
+      <c r="C4" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="76"/>
-      <c r="AD4" s="76"/>
-      <c r="AE4" s="76"/>
-      <c r="AF4" s="76"/>
-      <c r="AG4" s="76"/>
-      <c r="AH4" s="76"/>
-      <c r="AI4" s="76"/>
-      <c r="AJ4" s="76"/>
-      <c r="AK4" s="76"/>
-      <c r="AL4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="77"/>
+      <c r="W4" s="77"/>
+      <c r="X4" s="77"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
+      <c r="AB4" s="77"/>
+      <c r="AC4" s="77"/>
+      <c r="AD4" s="77"/>
+      <c r="AE4" s="77"/>
+      <c r="AF4" s="77"/>
+      <c r="AG4" s="77"/>
+      <c r="AH4" s="77"/>
+      <c r="AI4" s="77"/>
+      <c r="AJ4" s="77"/>
+      <c r="AK4" s="77"/>
+      <c r="AL4" s="78"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="75" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="76"/>
-      <c r="Y5" s="76"/>
-      <c r="Z5" s="76"/>
-      <c r="AA5" s="76"/>
-      <c r="AB5" s="76"/>
-      <c r="AC5" s="76"/>
-      <c r="AD5" s="76"/>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="76"/>
-      <c r="AJ5" s="76"/>
-      <c r="AK5" s="76"/>
-      <c r="AL5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
+      <c r="W5" s="77"/>
+      <c r="X5" s="77"/>
+      <c r="Y5" s="77"/>
+      <c r="Z5" s="77"/>
+      <c r="AA5" s="77"/>
+      <c r="AB5" s="77"/>
+      <c r="AC5" s="77"/>
+      <c r="AD5" s="77"/>
+      <c r="AE5" s="77"/>
+      <c r="AF5" s="77"/>
+      <c r="AG5" s="77"/>
+      <c r="AH5" s="77"/>
+      <c r="AI5" s="77"/>
+      <c r="AJ5" s="77"/>
+      <c r="AK5" s="77"/>
+      <c r="AL5" s="78"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="75" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="76"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
-      <c r="Z6" s="76"/>
-      <c r="AA6" s="76"/>
-      <c r="AB6" s="76"/>
-      <c r="AC6" s="76"/>
-      <c r="AD6" s="76"/>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="76"/>
-      <c r="AI6" s="76"/>
-      <c r="AJ6" s="76"/>
-      <c r="AK6" s="76"/>
-      <c r="AL6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
+      <c r="V6" s="77"/>
+      <c r="W6" s="77"/>
+      <c r="X6" s="77"/>
+      <c r="Y6" s="77"/>
+      <c r="Z6" s="77"/>
+      <c r="AA6" s="77"/>
+      <c r="AB6" s="77"/>
+      <c r="AC6" s="77"/>
+      <c r="AD6" s="77"/>
+      <c r="AE6" s="77"/>
+      <c r="AF6" s="77"/>
+      <c r="AG6" s="77"/>
+      <c r="AH6" s="77"/>
+      <c r="AI6" s="77"/>
+      <c r="AJ6" s="77"/>
+      <c r="AK6" s="77"/>
+      <c r="AL6" s="78"/>
     </row>
     <row r="7" spans="1:38" ht="100" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="79"/>
+      <c r="B7" s="80"/>
       <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
@@ -5679,7 +5678,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -5749,13 +5748,13 @@
         <v>138</v>
       </c>
       <c r="T3" s="26" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="U3" s="26" t="s">
         <v>501</v>
       </c>
       <c r="V3" s="27" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="15" thickTop="1" x14ac:dyDescent="0.35">
@@ -6384,7 +6383,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="T13" s="23" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
@@ -6394,17 +6393,17 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="16" x14ac:dyDescent="0.45">
       <c r="B18" s="69" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="H19" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>150</v>
@@ -6800,7 +6799,7 @@
         <v>689</v>
       </c>
       <c r="J30" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K30" s="42">
         <f>INDEX('BEA Data'!C:C,MATCH(TRIM('U.S. Data for ISIC Splits'!I30),'BEA Data'!E:E,0))</f>
@@ -9050,7 +9049,7 @@
         <v>67</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D87" s="42">
         <v>10489</v>
@@ -9866,7 +9865,7 @@
         <v>771</v>
       </c>
       <c r="J108" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="K108" s="42">
         <f>INDEX('BEA Data'!C:C,MATCH(TRIM('U.S. Data for ISIC Splits'!I108),'BEA Data'!E:E,0))</f>
@@ -10427,7 +10426,7 @@
         <v>113</v>
       </c>
       <c r="C133" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D133" s="42">
         <v>16519</v>
@@ -10847,7 +10846,7 @@
         <v>143</v>
       </c>
       <c r="C163" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D163" s="42">
         <v>23129</v>
@@ -11169,7 +11168,7 @@
         <v>166</v>
       </c>
       <c r="C186" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D186" s="42">
         <v>64775</v>
@@ -12009,7 +12008,7 @@
         <v>226</v>
       </c>
       <c r="C246" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D246" s="42">
         <v>69178</v>
@@ -12191,7 +12190,7 @@
         <v>239</v>
       </c>
       <c r="C259" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D259" s="42">
         <v>25121</v>
@@ -12373,7 +12372,7 @@
         <v>252</v>
       </c>
       <c r="C272" s="43" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D272" s="42">
         <v>40633</v>
@@ -14574,7 +14573,7 @@
         <v>409</v>
       </c>
       <c r="C429" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D429" s="42">
         <v>1457648</v>
@@ -14588,7 +14587,7 @@
         <v>410</v>
       </c>
       <c r="C430" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D430" s="42">
         <v>462628</v>
@@ -14602,7 +14601,7 @@
         <v>411</v>
       </c>
       <c r="C431" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D431" s="42">
         <v>1376800</v>
@@ -14725,7 +14724,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="67" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.4">
@@ -14740,7 +14739,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="62" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -14751,7 +14750,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -14770,7 +14769,7 @@
         <v>155</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C8" s="64">
         <v>29298013</v>
@@ -14785,7 +14784,7 @@
         <v>157</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C9" s="62">
         <v>15049121</v>
@@ -14800,7 +14799,7 @@
         <v>159</v>
       </c>
       <c r="B10" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C10" s="62">
         <v>1860444</v>
@@ -14815,7 +14814,7 @@
         <v>161</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C11" s="62">
         <v>12388448</v>
@@ -14845,7 +14844,7 @@
         <v>165</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C13" s="62">
         <v>12463662</v>
@@ -14860,7 +14859,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="62" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C14" s="62">
         <v>1905894</v>
@@ -14875,7 +14874,7 @@
         <v>169</v>
       </c>
       <c r="B15" s="62" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C15" s="62">
         <v>11632115</v>
@@ -14890,7 +14889,7 @@
         <v>171</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C16" s="64">
         <v>269686</v>
@@ -14905,7 +14904,7 @@
         <v>173</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C17" s="62">
         <v>80082</v>
@@ -14920,7 +14919,7 @@
         <v>175</v>
       </c>
       <c r="B18" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C18" s="62">
         <v>8148</v>
@@ -14935,7 +14934,7 @@
         <v>177</v>
       </c>
       <c r="B19" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C19" s="62">
         <v>181456</v>
@@ -14950,7 +14949,7 @@
         <v>179</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C20" s="64">
         <v>215830</v>
@@ -14965,7 +14964,7 @@
         <v>181</v>
       </c>
       <c r="B21" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C21" s="62">
         <v>44527</v>
@@ -14980,7 +14979,7 @@
         <v>183</v>
       </c>
       <c r="B22" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C22" s="62">
         <v>5548</v>
@@ -14995,7 +14994,7 @@
         <v>186</v>
       </c>
       <c r="B23" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C23" s="62">
         <v>165755</v>
@@ -15010,7 +15009,7 @@
         <v>188</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C24" s="64">
         <v>53856</v>
@@ -15025,7 +15024,7 @@
         <v>190</v>
       </c>
       <c r="B25" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C25" s="62">
         <v>35555</v>
@@ -15040,7 +15039,7 @@
         <v>192</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C26" s="62">
         <v>2600</v>
@@ -15055,7 +15054,7 @@
         <v>194</v>
       </c>
       <c r="B27" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C27" s="62">
         <v>15701</v>
@@ -15070,7 +15069,7 @@
         <v>196</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C28" s="64">
         <v>404248</v>
@@ -15085,7 +15084,7 @@
         <v>198</v>
       </c>
       <c r="B29" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C29" s="62">
         <v>92465</v>
@@ -15100,7 +15099,7 @@
         <v>201</v>
       </c>
       <c r="B30" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C30" s="62">
         <v>60004</v>
@@ -15115,7 +15114,7 @@
         <v>203</v>
       </c>
       <c r="B31" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C31" s="62">
         <v>251778</v>
@@ -15130,7 +15129,7 @@
         <v>205</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C32" s="64">
         <v>252608</v>
@@ -15145,7 +15144,7 @@
         <v>207</v>
       </c>
       <c r="B33" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C33" s="62">
         <v>31824</v>
@@ -15160,7 +15159,7 @@
         <v>209</v>
       </c>
       <c r="B34" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C34" s="62">
         <v>49110</v>
@@ -15175,7 +15174,7 @@
         <v>211</v>
       </c>
       <c r="B35" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C35" s="62">
         <v>171675</v>
@@ -15190,7 +15189,7 @@
         <v>213</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C36" s="64">
         <v>80799</v>
@@ -15205,7 +15204,7 @@
         <v>215</v>
       </c>
       <c r="B37" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C37" s="62">
         <v>23658</v>
@@ -15220,7 +15219,7 @@
         <v>217</v>
       </c>
       <c r="B38" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C38" s="62">
         <v>7977</v>
@@ -15235,7 +15234,7 @@
         <v>219</v>
       </c>
       <c r="B39" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C39" s="62">
         <v>49165</v>
@@ -15250,7 +15249,7 @@
         <v>222</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C40" s="64">
         <v>70840</v>
@@ -15265,7 +15264,7 @@
         <v>225</v>
       </c>
       <c r="B41" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C41" s="62">
         <v>36984</v>
@@ -15280,7 +15279,7 @@
         <v>227</v>
       </c>
       <c r="B42" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C42" s="62">
         <v>2917</v>
@@ -15295,7 +15294,7 @@
         <v>229</v>
       </c>
       <c r="B43" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C43" s="62">
         <v>30939</v>
@@ -15310,7 +15309,7 @@
         <v>231</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C44" s="64">
         <v>454357</v>
@@ -15325,7 +15324,7 @@
         <v>233</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C45" s="62">
         <v>103431</v>
@@ -15340,7 +15339,7 @@
         <v>235</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C46" s="62">
         <v>85222</v>
@@ -15355,7 +15354,7 @@
         <v>237</v>
       </c>
       <c r="B47" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C47" s="62">
         <v>265705</v>
@@ -15370,7 +15369,7 @@
         <v>239</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C48" s="64">
         <v>1305402</v>
@@ -15385,7 +15384,7 @@
         <v>241</v>
       </c>
       <c r="B49" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C49" s="62">
         <v>799308</v>
@@ -15400,7 +15399,7 @@
         <v>243</v>
       </c>
       <c r="B50" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C50" s="62">
         <v>14907</v>
@@ -15415,7 +15414,7 @@
         <v>245</v>
       </c>
       <c r="B51" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C51" s="62">
         <v>491187</v>
@@ -15430,7 +15429,7 @@
         <v>247</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C52" s="64">
         <v>2880724</v>
@@ -15445,7 +15444,7 @@
         <v>249</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C53" s="62">
         <v>1359135</v>
@@ -15460,7 +15459,7 @@
         <v>251</v>
       </c>
       <c r="B54" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C54" s="62">
         <v>106009</v>
@@ -15475,7 +15474,7 @@
         <v>253</v>
       </c>
       <c r="B55" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C55" s="62">
         <v>1415581</v>
@@ -15490,7 +15489,7 @@
         <v>255</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C56" s="64">
         <v>1524841</v>
@@ -15505,7 +15504,7 @@
         <v>257</v>
       </c>
       <c r="B57" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C57" s="62">
         <v>893038</v>
@@ -15520,7 +15519,7 @@
         <v>260</v>
       </c>
       <c r="B58" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C58" s="62">
         <v>43401</v>
@@ -15535,7 +15534,7 @@
         <v>263</v>
       </c>
       <c r="B59" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C59" s="62">
         <v>588402</v>
@@ -15550,7 +15549,7 @@
         <v>265</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C60" s="64">
         <v>60171</v>
@@ -15565,7 +15564,7 @@
         <v>267</v>
       </c>
       <c r="B61" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C61" s="62">
         <v>32297</v>
@@ -15580,7 +15579,7 @@
         <v>269</v>
       </c>
       <c r="B62" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C62" s="62">
         <v>1132</v>
@@ -15595,7 +15594,7 @@
         <v>271</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C63" s="62">
         <v>26742</v>
@@ -15610,7 +15609,7 @@
         <v>273</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C64" s="64">
         <v>77516</v>
@@ -15625,7 +15624,7 @@
         <v>275</v>
       </c>
       <c r="B65" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C65" s="62">
         <v>38942</v>
@@ -15640,7 +15639,7 @@
         <v>277</v>
       </c>
       <c r="B66" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C66" s="62">
         <v>2209</v>
@@ -15655,7 +15654,7 @@
         <v>279</v>
       </c>
       <c r="B67" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C67" s="62">
         <v>36365</v>
@@ -15670,7 +15669,7 @@
         <v>281</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C68" s="64">
         <v>76516</v>
@@ -15685,7 +15684,7 @@
         <v>283</v>
       </c>
       <c r="B69" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C69" s="62">
         <v>41277</v>
@@ -15700,7 +15699,7 @@
         <v>286</v>
       </c>
       <c r="B70" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C70" s="62">
         <v>3553</v>
@@ -15715,7 +15714,7 @@
         <v>288</v>
       </c>
       <c r="B71" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C71" s="62">
         <v>31686</v>
@@ -15730,7 +15729,7 @@
         <v>291</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C72" s="64">
         <v>190535</v>
@@ -15745,7 +15744,7 @@
         <v>293</v>
       </c>
       <c r="B73" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C73" s="62">
         <v>128099</v>
@@ -15760,7 +15759,7 @@
         <v>295</v>
       </c>
       <c r="B74" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C74" s="62">
         <v>5721</v>
@@ -15775,7 +15774,7 @@
         <v>296</v>
       </c>
       <c r="B75" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C75" s="62">
         <v>56715</v>
@@ -15790,7 +15789,7 @@
         <v>298</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C76" s="64">
         <v>208621</v>
@@ -15805,7 +15804,7 @@
         <v>300</v>
       </c>
       <c r="B77" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C77" s="62">
         <v>120012</v>
@@ -15820,7 +15819,7 @@
         <v>302</v>
       </c>
       <c r="B78" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C78" s="62">
         <v>5159</v>
@@ -15835,7 +15834,7 @@
         <v>304</v>
       </c>
       <c r="B79" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C79" s="62">
         <v>83450</v>
@@ -15850,7 +15849,7 @@
         <v>306</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C80" s="64">
         <v>299783</v>
@@ -15865,7 +15864,7 @@
         <v>308</v>
       </c>
       <c r="B81" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C81" s="62">
         <v>187376</v>
@@ -15880,7 +15879,7 @@
         <v>310</v>
       </c>
       <c r="B82" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C82" s="62">
         <v>11837</v>
@@ -15895,7 +15894,7 @@
         <v>312</v>
       </c>
       <c r="B83" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C83" s="62">
         <v>100569</v>
@@ -15910,7 +15909,7 @@
         <v>314</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C84" s="64">
         <v>80171</v>
@@ -15925,7 +15924,7 @@
         <v>316</v>
       </c>
       <c r="B85" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C85" s="62">
         <v>47290</v>
@@ -15940,7 +15939,7 @@
         <v>318</v>
       </c>
       <c r="B86" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C86" s="62">
         <v>1139</v>
@@ -15955,7 +15954,7 @@
         <v>320</v>
       </c>
       <c r="B87" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C87" s="62">
         <v>31742</v>
@@ -15970,7 +15969,7 @@
         <v>322</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C88" s="64">
         <v>185854</v>
@@ -15985,7 +15984,7 @@
         <v>324</v>
       </c>
       <c r="B89" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C89" s="62">
         <v>96593</v>
@@ -16000,7 +15999,7 @@
         <v>326</v>
       </c>
       <c r="B90" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C90" s="62">
         <v>5277</v>
@@ -16015,7 +16014,7 @@
         <v>328</v>
       </c>
       <c r="B91" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C91" s="62">
         <v>83984</v>
@@ -16030,7 +16029,7 @@
         <v>330</v>
       </c>
       <c r="B92" s="64" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C92" s="64">
         <v>197330</v>
@@ -16045,7 +16044,7 @@
         <v>332</v>
       </c>
       <c r="B93" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C93" s="62">
         <v>106326</v>
@@ -16060,7 +16059,7 @@
         <v>334</v>
       </c>
       <c r="B94" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C94" s="62">
         <v>4107</v>
@@ -16075,7 +16074,7 @@
         <v>336</v>
       </c>
       <c r="B95" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C95" s="62">
         <v>86897</v>
@@ -16090,7 +16089,7 @@
         <v>338</v>
       </c>
       <c r="B96" s="64" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C96" s="64">
         <v>34448</v>
@@ -16105,7 +16104,7 @@
         <v>340</v>
       </c>
       <c r="B97" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C97" s="62">
         <v>25178</v>
@@ -16120,7 +16119,7 @@
         <v>342</v>
       </c>
       <c r="B98" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C98" s="62">
         <v>584</v>
@@ -16135,7 +16134,7 @@
         <v>344</v>
       </c>
       <c r="B99" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C99" s="62">
         <v>8686</v>
@@ -16150,7 +16149,7 @@
         <v>346</v>
       </c>
       <c r="B100" s="64" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C100" s="64">
         <v>113897</v>
@@ -16165,7 +16164,7 @@
         <v>348</v>
       </c>
       <c r="B101" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C101" s="62">
         <v>69647</v>
@@ -16180,7 +16179,7 @@
         <v>350</v>
       </c>
       <c r="B102" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C102" s="62">
         <v>2683</v>
@@ -16195,7 +16194,7 @@
         <v>352</v>
       </c>
       <c r="B103" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C103" s="62">
         <v>41566</v>
@@ -16210,7 +16209,7 @@
         <v>354</v>
       </c>
       <c r="B104" s="64" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C104" s="64">
         <v>1355884</v>
@@ -16222,10 +16221,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="62" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B105" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C105" s="62">
         <v>466097</v>
@@ -16237,10 +16236,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="62" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B106" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C106" s="62">
         <v>62608</v>
@@ -16252,10 +16251,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="62" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B107" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C107" s="62">
         <v>827179</v>
@@ -16267,10 +16266,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="62" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B108" s="64" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C108" s="64">
         <v>360176</v>
@@ -16282,10 +16281,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="62" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B109" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C109" s="62">
         <v>160356</v>
@@ -16297,10 +16296,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="62" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B110" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C110" s="62">
         <v>23601</v>
@@ -16312,10 +16311,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="62" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B111" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C111" s="62">
         <v>176219</v>
@@ -16327,10 +16326,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="62" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B112" s="64" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C112" s="64">
         <v>16316</v>
@@ -16342,10 +16341,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="62" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B113" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C113" s="62">
         <v>12641</v>
@@ -16357,10 +16356,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="62" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B114" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C114" s="62">
         <v>810</v>
@@ -16372,10 +16371,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="62" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B115" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C115" s="62">
         <v>2865</v>
@@ -16387,10 +16386,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="62" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B116" s="64" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C116" s="64">
         <v>12453</v>
@@ -16402,10 +16401,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="62" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B117" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C117" s="62">
         <v>7740</v>
@@ -16417,10 +16416,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="62" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B118" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C118" s="62">
         <v>403</v>
@@ -16432,10 +16431,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="62" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B119" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C119" s="62">
         <v>4310</v>
@@ -16447,10 +16446,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="62" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B120" s="64" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C120" s="64">
         <v>74433</v>
@@ -16462,10 +16461,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="62" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B121" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C121" s="62">
         <v>36515</v>
@@ -16477,10 +16476,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="62" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B122" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C122" s="62">
         <v>2505</v>
@@ -16492,10 +16491,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="62" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B123" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C123" s="62">
         <v>35413</v>
@@ -16507,10 +16506,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="62" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B124" s="64" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C124" s="64">
         <v>41301</v>
@@ -16522,10 +16521,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="62" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B125" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C125" s="62">
         <v>26845</v>
@@ -16537,10 +16536,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="62" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B126" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C126" s="62">
         <v>1058</v>
@@ -16552,10 +16551,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="62" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B127" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C127" s="62">
         <v>13399</v>
@@ -16567,10 +16566,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="62" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B128" s="64" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C128" s="64">
         <v>195712</v>
@@ -16582,10 +16581,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="62" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B129" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C129" s="62">
         <v>22688</v>
@@ -16597,10 +16596,10 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="62" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B130" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C130" s="62">
         <v>6274</v>
@@ -16612,10 +16611,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="62" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B131" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C131" s="62">
         <v>166750</v>
@@ -16627,10 +16626,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="62" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B132" s="64" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C132" s="64">
         <v>554021</v>
@@ -16642,10 +16641,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="62" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B133" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C133" s="62">
         <v>136974</v>
@@ -16657,10 +16656,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="62" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B134" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C134" s="62">
         <v>24681</v>
@@ -16672,10 +16671,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="62" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B135" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C135" s="62">
         <v>392366</v>
@@ -16687,10 +16686,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="62" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B136" s="64" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C136" s="64">
         <v>101471</v>
@@ -16702,10 +16701,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="62" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B137" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C137" s="62">
         <v>62338</v>
@@ -16717,10 +16716,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="62" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B138" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C138" s="62">
         <v>3276</v>
@@ -16732,10 +16731,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="62" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B139" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C139" s="62">
         <v>35857</v>
@@ -16747,10 +16746,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="62" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B140" s="64" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C140" s="64">
         <v>1706289</v>
@@ -16762,10 +16761,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="62" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B141" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C141" s="62">
         <v>733047</v>
@@ -16777,10 +16776,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="62" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B142" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C142" s="62">
         <v>328298</v>
@@ -16792,10 +16791,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="62" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B143" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C143" s="62">
         <v>644944</v>
@@ -16807,10 +16806,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="62" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B144" s="64" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C144" s="64">
         <v>1849039</v>
@@ -16822,10 +16821,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="62" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B145" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C145" s="62">
         <v>846090</v>
@@ -16837,10 +16836,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="62" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B146" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C146" s="62">
         <v>338218</v>
@@ -16852,10 +16851,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="62" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B147" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C147" s="62">
         <v>664731</v>
@@ -16867,10 +16866,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="62" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B148" s="64" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C148" s="64">
         <v>356851</v>
@@ -16882,10 +16881,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="62" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B149" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C149" s="62">
         <v>172609</v>
@@ -16897,10 +16896,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="62" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B150" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C150" s="62">
         <v>70686</v>
@@ -16912,10 +16911,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="62" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B151" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C151" s="62">
         <v>113557</v>
@@ -16927,10 +16926,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="62" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B152" s="64" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C152" s="64">
         <v>236132</v>
@@ -16942,10 +16941,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="62" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B153" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C153" s="62">
         <v>138881</v>
@@ -16957,10 +16956,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="62" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B154" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C154" s="62">
         <v>37153</v>
@@ -16972,10 +16971,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="62" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B155" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C155" s="62">
         <v>60098</v>
@@ -16987,10 +16986,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="62" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B156" s="64" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C156" s="64">
         <v>224084</v>
@@ -17002,10 +17001,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="62" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B157" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C157" s="62">
         <v>126489</v>
@@ -17017,10 +17016,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="62" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B158" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C158" s="62">
         <v>57632</v>
@@ -17032,10 +17031,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="62" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B159" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C159" s="62">
         <v>39963</v>
@@ -17047,10 +17046,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="62" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B160" s="64" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C160" s="64">
         <v>1031973</v>
@@ -17062,10 +17061,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="62" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B161" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C161" s="62">
         <v>408112</v>
@@ -17077,10 +17076,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="62" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B162" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C162" s="62">
         <v>172747</v>
@@ -17092,10 +17091,10 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="62" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B163" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C163" s="62">
         <v>451114</v>
@@ -17107,10 +17106,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="62" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B164" s="64" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C164" s="64">
         <v>987302</v>
@@ -17122,10 +17121,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="62" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B165" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C165" s="62">
         <v>577240</v>
@@ -17137,10 +17136,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="62" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B166" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C166" s="62">
         <v>54055</v>
@@ -17152,10 +17151,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="62" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B167" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C167" s="62">
         <v>356007</v>
@@ -17167,10 +17166,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="62" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B168" s="64" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C168" s="64">
         <v>175712</v>
@@ -17182,10 +17181,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="62" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B169" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C169" s="62">
         <v>88114</v>
@@ -17197,10 +17196,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="62" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B170" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C170" s="62">
         <v>34858</v>
@@ -17212,10 +17211,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="62" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B171" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C171" s="62">
         <v>52740</v>
@@ -17227,10 +17226,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="62" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B172" s="64" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C172" s="64">
         <v>53169</v>
@@ -17242,10 +17241,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="62" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B173" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C173" s="62">
         <v>26365</v>
@@ -17257,10 +17256,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="62" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B174" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C174" s="62">
         <v>-1855</v>
@@ -17272,10 +17271,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="62" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B175" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C175" s="62">
         <v>28659</v>
@@ -17287,10 +17286,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="62" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B176" s="64" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C176" s="64">
         <v>24335</v>
@@ -17302,10 +17301,10 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="62" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B177" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C177" s="62">
         <v>9882</v>
@@ -17317,10 +17316,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="62" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B178" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C178" s="62">
         <v>1529</v>
@@ -17332,10 +17331,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="62" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B179" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C179" s="62">
         <v>12924</v>
@@ -17347,10 +17346,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="62" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B180" s="64" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C180" s="64">
         <v>257356</v>
@@ -17362,10 +17361,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="62" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B181" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C181" s="62">
         <v>135191</v>
@@ -17377,10 +17376,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="62" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B182" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C182" s="62">
         <v>6408</v>
@@ -17392,10 +17391,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="62" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B183" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C183" s="62">
         <v>115757</v>
@@ -17407,10 +17406,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="62" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B184" s="64" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C184" s="64">
         <v>83850</v>
@@ -17422,10 +17421,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="62" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B185" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C185" s="62">
         <v>37736</v>
@@ -17437,10 +17436,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="62" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B186" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C186" s="62">
         <v>3057</v>
@@ -17452,10 +17451,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="62" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B187" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C187" s="62">
         <v>43057</v>
@@ -17467,10 +17466,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="62" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B188" s="64" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C188" s="64">
         <v>48501</v>
@@ -17482,10 +17481,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="62" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B189" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C189" s="62">
         <v>10719</v>
@@ -17497,10 +17496,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="62" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B190" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C190" s="62">
         <v>4919</v>
@@ -17512,10 +17511,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="62" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B191" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C191" s="62">
         <v>32862</v>
@@ -17527,10 +17526,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="62" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B192" s="64" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C192" s="64">
         <v>216231</v>
@@ -17542,10 +17541,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="62" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B193" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C193" s="62">
         <v>147652</v>
@@ -17557,10 +17556,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="62" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B194" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C194" s="62">
         <v>3695</v>
@@ -17572,10 +17571,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="62" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B195" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C195" s="62">
         <v>64884</v>
@@ -17587,10 +17586,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="62" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B196" s="64" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C196" s="64">
         <v>128148</v>
@@ -17602,10 +17601,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="62" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B197" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C197" s="62">
         <v>121581</v>
@@ -17617,10 +17616,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="62" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B198" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C198" s="62">
         <v>1443</v>
@@ -17632,10 +17631,10 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="62" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B199" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C199" s="62">
         <v>5124</v>
@@ -17647,10 +17646,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="62" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B200" s="64" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C200" s="64">
         <v>1592692</v>
@@ -17662,10 +17661,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="62" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B201" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C201" s="62">
         <v>593157</v>
@@ -17677,10 +17676,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="62" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B202" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C202" s="62">
         <v>65934</v>
@@ -17692,10 +17691,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="62" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B203" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C203" s="62">
         <v>933601</v>
@@ -17707,10 +17706,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="62" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B204" s="64" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C204" s="64">
         <v>442706</v>
@@ -17722,10 +17721,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="62" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B205" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C205" s="62">
         <v>184170</v>
@@ -17737,10 +17736,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="62" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B206" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C206" s="62">
         <v>8289</v>
@@ -17752,10 +17751,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="62" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B207" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C207" s="62">
         <v>250247</v>
@@ -17767,10 +17766,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="62" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B208" s="64" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C208" s="64">
         <v>119385</v>
@@ -17782,10 +17781,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="62" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B209" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C209" s="62">
         <v>42580</v>
@@ -17797,10 +17796,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="62" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B210" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C210" s="62">
         <v>6792</v>
@@ -17812,10 +17811,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="62" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B211" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C211" s="62">
         <v>70014</v>
@@ -17827,10 +17826,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="62" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B212" s="64" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C212" s="64">
         <v>501545</v>
@@ -17842,10 +17841,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="62" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B213" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C213" s="62">
         <v>129892</v>
@@ -17857,10 +17856,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="62" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B214" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C214" s="62">
         <v>42372</v>
@@ -17872,10 +17871,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="62" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B215" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C215" s="62">
         <v>329281</v>
@@ -17887,10 +17886,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="62" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B216" s="64" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C216" s="64">
         <v>529056</v>
@@ -17902,10 +17901,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="62" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B217" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C217" s="62">
         <v>236515</v>
@@ -17920,7 +17919,7 @@
         <v>100</v>
       </c>
       <c r="B218" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C218" s="62">
         <v>8482</v>
@@ -17932,10 +17931,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="62" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B219" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C219" s="62">
         <v>284059</v>
@@ -17947,10 +17946,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="62" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B220" s="64" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C220" s="64">
         <v>6281555</v>
@@ -17962,10 +17961,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="62" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B221" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C221" s="62">
         <v>1338953</v>
@@ -17977,10 +17976,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="62" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B222" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C222" s="62">
         <v>483266</v>
@@ -17992,10 +17991,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B223" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C223" s="62">
         <v>4459335</v>
@@ -18007,10 +18006,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="62" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B224" s="64" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C224" s="64">
         <v>2229155</v>
@@ -18022,10 +18021,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="62" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B225" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C225" s="62">
         <v>1115372</v>
@@ -18037,10 +18036,10 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="62" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B226" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C226" s="62">
         <v>83485</v>
@@ -18052,10 +18051,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="62" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B227" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C227" s="62">
         <v>1030298</v>
@@ -18067,10 +18066,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="62" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B228" s="64" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C228" s="64">
         <v>1013285</v>
@@ -18082,10 +18081,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="62" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B229" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C229" s="62">
         <v>354009</v>
@@ -18097,10 +18096,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="62" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B230" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C230" s="62">
         <v>26036</v>
@@ -18112,10 +18111,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="62" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B231" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C231" s="62">
         <v>633241</v>
@@ -18127,10 +18126,10 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="62" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B232" s="64" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C232" s="64">
         <v>396082</v>
@@ -18142,10 +18141,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="62" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B233" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C233" s="62">
         <v>364518</v>
@@ -18157,10 +18156,10 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="62" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B234" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C234" s="62">
         <v>8296</v>
@@ -18172,10 +18171,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="62" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B235" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C235" s="62">
         <v>23268</v>
@@ -18187,10 +18186,10 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="62" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B236" s="64" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C236" s="64">
         <v>791806</v>
@@ -18202,10 +18201,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="62" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B237" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C237" s="62">
         <v>390088</v>
@@ -18217,10 +18216,10 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="62" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B238" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C238" s="62">
         <v>48317</v>
@@ -18232,10 +18231,10 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="62" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B239" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C239" s="62">
         <v>353401</v>
@@ -18247,10 +18246,10 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="62" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B240" s="64" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C240" s="64">
         <v>27981</v>
@@ -18262,10 +18261,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="62" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B241" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C241" s="62">
         <v>6758</v>
@@ -18277,10 +18276,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="62" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B242" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C242" s="62">
         <v>835</v>
@@ -18292,10 +18291,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="62" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B243" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C243" s="62">
         <v>20388</v>
@@ -18307,10 +18306,10 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="62" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B244" s="64" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C244" s="64">
         <v>4052400</v>
@@ -18322,10 +18321,10 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="62" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B245" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C245" s="62">
         <v>223581</v>
@@ -18337,10 +18336,10 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="62" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B246" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C246" s="62">
         <v>399782</v>
@@ -18352,10 +18351,10 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="62" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B247" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C247" s="62">
         <v>3429038</v>
@@ -18367,10 +18366,10 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="62" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B248" s="64" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C248" s="64">
         <v>3684230</v>
@@ -18382,10 +18381,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="62" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B249" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C249" s="62">
         <v>172074</v>
@@ -18397,10 +18396,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="62" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B250" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C250" s="62">
         <v>367940</v>
@@ -18412,10 +18411,10 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="62" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B251" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C251" s="62">
         <v>3144216</v>
@@ -18427,10 +18426,10 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="62" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B252" s="64" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C252" s="64">
         <v>2853988</v>
@@ -18442,10 +18441,10 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="62" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B253" s="62" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C253" s="62">
         <v>28487</v>
@@ -18457,10 +18456,10 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="62" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B254" s="62" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C254" s="62">
         <v>327118</v>
@@ -18472,10 +18471,10 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="62" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B255" s="62" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C255" s="62">
         <v>2498383</v>
@@ -18487,10 +18486,10 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="62" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B256" s="64" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C256" s="64">
         <v>830242</v>
@@ -18502,10 +18501,10 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="62" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B257" s="62" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C257" s="62">
         <v>143587</v>
@@ -18517,10 +18516,10 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="62" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B258" s="62" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C258" s="62">
         <v>40822</v>
@@ -18532,10 +18531,10 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="62" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B259" s="62" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C259" s="62">
         <v>645833</v>
@@ -18547,10 +18546,10 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="62" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B260" s="64" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C260" s="64">
         <v>368169</v>
@@ -18562,10 +18561,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="62" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B261" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C261" s="62">
         <v>51506</v>
@@ -18577,10 +18576,10 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="62" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B262" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C262" s="62">
         <v>31841</v>
@@ -18592,10 +18591,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="62" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B263" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C263" s="62">
         <v>284822</v>
@@ -18607,10 +18606,10 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="62" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B264" s="64" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C264" s="64">
         <v>3811104</v>
@@ -18622,10 +18621,10 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="62" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B265" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C265" s="62">
         <v>2726576</v>
@@ -18637,10 +18636,10 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" s="62" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B266" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C266" s="62">
         <v>93608</v>
@@ -18652,10 +18651,10 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" s="62" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B267" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C267" s="62">
         <v>990920</v>
@@ -18667,10 +18666,10 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="62" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B268" s="64" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C268" s="64">
         <v>2355069</v>
@@ -18682,10 +18681,10 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="62" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B269" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C269" s="62">
         <v>1606279</v>
@@ -18697,10 +18696,10 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="62" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B270" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C270" s="62">
         <v>59386</v>
@@ -18712,10 +18711,10 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="62" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B271" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C271" s="62">
         <v>689404</v>
@@ -18727,10 +18726,10 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" s="62" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B272" s="64" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C272" s="64">
         <v>387719</v>
@@ -18742,10 +18741,10 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" s="62" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B273" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C273" s="62">
         <v>188351</v>
@@ -18757,10 +18756,10 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="62" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B274" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C274" s="62">
         <v>23296</v>
@@ -18772,10 +18771,10 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" s="62" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B275" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C275" s="62">
         <v>176072</v>
@@ -18787,10 +18786,10 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" s="62" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B276" s="64" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C276" s="64">
         <v>522249</v>
@@ -18802,10 +18801,10 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="62" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B277" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C277" s="62">
         <v>445176</v>
@@ -18817,10 +18816,10 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="62" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B278" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C278" s="62">
         <v>12128</v>
@@ -18832,10 +18831,10 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="62" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B279" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C279" s="62">
         <v>64945</v>
@@ -18847,10 +18846,10 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="62" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B280" s="64" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C280" s="64">
         <v>1445101</v>
@@ -18862,10 +18861,10 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" s="62" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B281" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C281" s="62">
         <v>972752</v>
@@ -18877,10 +18876,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" s="62" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B282" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C282" s="62">
         <v>23961</v>
@@ -18892,10 +18891,10 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="62" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B283" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C283" s="62">
         <v>448387</v>
@@ -18907,10 +18906,10 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="62" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B284" s="64" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C284" s="64">
         <v>544333</v>
@@ -18922,10 +18921,10 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="62" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B285" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C285" s="62">
         <v>482843</v>
@@ -18937,10 +18936,10 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="62" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B286" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C286" s="62">
         <v>12879</v>
@@ -18952,10 +18951,10 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="62" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B287" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C287" s="62">
         <v>48611</v>
@@ -18967,10 +18966,10 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="62" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B288" s="64" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C288" s="64">
         <v>911703</v>
@@ -18982,10 +18981,10 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="62" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B289" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C289" s="62">
         <v>637453</v>
@@ -18997,10 +18996,10 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="62" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B290" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C290" s="62">
         <v>21344</v>
@@ -19012,10 +19011,10 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="62" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B291" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C291" s="62">
         <v>252905</v>
@@ -19027,10 +19026,10 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="62" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B292" s="64" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C292" s="64">
         <v>823102</v>
@@ -19042,10 +19041,10 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" s="62" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B293" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C293" s="62">
         <v>587967</v>
@@ -19057,10 +19056,10 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="62" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B294" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C294" s="62">
         <v>15842</v>
@@ -19072,10 +19071,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="62" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B295" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C295" s="62">
         <v>219292</v>
@@ -19087,10 +19086,10 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="62" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B296" s="64" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C296" s="64">
         <v>88601</v>
@@ -19102,10 +19101,10 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="62" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B297" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C297" s="62">
         <v>49486</v>
@@ -19117,10 +19116,10 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="62" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B298" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C298" s="62">
         <v>5501</v>
@@ -19132,10 +19131,10 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="62" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B299" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C299" s="62">
         <v>33613</v>
@@ -19147,10 +19146,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="62" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B300" s="64" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C300" s="64">
         <v>2544166</v>
@@ -19162,10 +19161,10 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="62" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B301" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C301" s="62">
         <v>2039440</v>
@@ -19177,10 +19176,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="62" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B302" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C302" s="62">
         <v>57305</v>
@@ -19192,10 +19191,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="62" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B303" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C303" s="62">
         <v>447422</v>
@@ -19207,10 +19206,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="62" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B304" s="64" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C304" s="64">
         <v>334785</v>
@@ -19222,10 +19221,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="62" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B305" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C305" s="62">
         <v>268002</v>
@@ -19237,10 +19236,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="62" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B306" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C306" s="62">
         <v>13386</v>
@@ -19252,10 +19251,10 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="62" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B307" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C307" s="62">
         <v>53397</v>
@@ -19267,10 +19266,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="62" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B308" s="64" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C308" s="64">
         <v>2209381</v>
@@ -19282,10 +19281,10 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="62" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B309" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C309" s="62">
         <v>1771438</v>
@@ -19297,10 +19296,10 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="62" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B310" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C310" s="62">
         <v>43919</v>
@@ -19312,10 +19311,10 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="62" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B311" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C311" s="62">
         <v>394025</v>
@@ -19327,10 +19326,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="62" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B312" s="64" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C312" s="64">
         <v>1078954</v>
@@ -19342,10 +19341,10 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="62" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B313" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C313" s="62">
         <v>816417</v>
@@ -19357,10 +19356,10 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="62" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B314" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C314" s="62">
         <v>13314</v>
@@ -19372,10 +19371,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="62" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B315" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C315" s="62">
         <v>249222</v>
@@ -19387,10 +19386,10 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="62" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B316" s="64" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C316" s="64">
         <v>691481</v>
@@ -19402,10 +19401,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="62" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B317" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C317" s="62">
         <v>561566</v>
@@ -19417,10 +19416,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="62" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B318" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C318" s="62">
         <v>21070</v>
@@ -19432,10 +19431,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" s="62" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B319" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C319" s="62">
         <v>108844</v>
@@ -19447,10 +19446,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="62" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B320" s="64" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C320" s="64">
         <v>212314</v>
@@ -19462,10 +19461,10 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="62" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B321" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C321" s="62">
         <v>188682</v>
@@ -19477,10 +19476,10 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="62" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B322" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C322" s="62">
         <v>9511</v>
@@ -19492,10 +19491,10 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="62" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B323" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C323" s="62">
         <v>14121</v>
@@ -19507,10 +19506,10 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="62" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B324" s="64" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C324" s="64">
         <v>226633</v>
@@ -19522,10 +19521,10 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="62" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B325" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C325" s="62">
         <v>204772</v>
@@ -19537,10 +19536,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="62" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B326" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C326" s="62">
         <v>24</v>
@@ -19552,10 +19551,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="62" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B327" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C327" s="62">
         <v>21837</v>
@@ -19567,10 +19566,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="62" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B328" s="64" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C328" s="64">
         <v>1287121</v>
@@ -19582,10 +19581,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="62" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B329" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C329" s="62">
         <v>737085</v>
@@ -19597,10 +19596,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="62" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B330" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C330" s="62">
         <v>175157</v>
@@ -19612,10 +19611,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="62" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B331" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C331" s="62">
         <v>374880</v>
@@ -19627,10 +19626,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="62" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B332" s="64" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C332" s="64">
         <v>326765</v>
@@ -19642,10 +19641,10 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="62" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B333" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C333" s="62">
         <v>170175</v>
@@ -19657,10 +19656,10 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="62" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B334" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C334" s="62">
         <v>38879</v>
@@ -19672,10 +19671,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="62" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B335" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C335" s="62">
         <v>117712</v>
@@ -19687,10 +19686,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="62" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B336" s="64" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C336" s="64">
         <v>190761</v>
@@ -19702,10 +19701,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="62" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B337" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C337" s="62">
         <v>88859</v>
@@ -19717,10 +19716,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="62" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B338" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C338" s="62">
         <v>10595</v>
@@ -19732,10 +19731,10 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="62" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B339" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C339" s="62">
         <v>91307</v>
@@ -19747,10 +19746,10 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="62" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B340" s="64" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C340" s="64">
         <v>136004</v>
@@ -19762,10 +19761,10 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="62" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B341" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C341" s="62">
         <v>81316</v>
@@ -19777,10 +19776,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="62" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B342" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C342" s="62">
         <v>28284</v>
@@ -19792,10 +19791,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="62" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B343" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C343" s="62">
         <v>26404</v>
@@ -19807,10 +19806,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="62" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B344" s="64" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C344" s="64">
         <v>960356</v>
@@ -19822,10 +19821,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="62" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B345" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C345" s="62">
         <v>566910</v>
@@ -19837,10 +19836,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="62" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B346" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C346" s="62">
         <v>136278</v>
@@ -19852,10 +19851,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="62" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B347" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C347" s="62">
         <v>257168</v>
@@ -19867,10 +19866,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="62" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B348" s="64" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C348" s="64">
         <v>257248</v>
@@ -19882,10 +19881,10 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="62" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B349" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C349" s="62">
         <v>108160</v>
@@ -19897,10 +19896,10 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="62" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B350" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C350" s="62">
         <v>47232</v>
@@ -19912,10 +19911,10 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="62" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B351" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C351" s="62">
         <v>101857</v>
@@ -19927,10 +19926,10 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="62" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B352" s="64" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C352" s="64">
         <v>703108</v>
@@ -19942,10 +19941,10 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="62" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B353" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C353" s="62">
         <v>458750</v>
@@ -19957,10 +19956,10 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="62" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B354" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C354" s="62">
         <v>89045</v>
@@ -19972,10 +19971,10 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="62" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B355" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C355" s="62">
         <v>155312</v>
@@ -19987,10 +19986,10 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="62" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B356" s="64" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C356" s="64">
         <v>627985</v>
@@ -20002,10 +20001,10 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="62" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B357" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C357" s="62">
         <v>437654</v>
@@ -20017,10 +20016,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="62" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B358" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C358" s="62">
         <v>35764</v>
@@ -20032,10 +20031,10 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="62" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B359" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C359" s="62">
         <v>154567</v>
@@ -20047,7 +20046,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="62" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B360" s="64" t="s">
         <v>772</v>
@@ -20062,10 +20061,10 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="62" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B361" s="62" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C361" s="62">
         <v>2585459</v>
@@ -20077,10 +20076,10 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="62" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B362" s="62" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C362" s="62">
         <v>-45450</v>
@@ -20092,10 +20091,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="62" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B363" s="62" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C363" s="62">
         <v>756333</v>
@@ -20107,10 +20106,10 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="62" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B364" s="64" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C364" s="64">
         <v>1064857</v>
@@ -20122,10 +20121,10 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="62" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B365" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C365" s="62">
         <v>680171</v>
@@ -20137,10 +20136,10 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="62" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B366" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C366" s="62">
         <v>-6847</v>
@@ -20152,10 +20151,10 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="62" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B367" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C367" s="62">
         <v>391533</v>
@@ -20167,10 +20166,10 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="62" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B368" s="64" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C368" s="64">
         <v>986778</v>
@@ -20182,10 +20181,10 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="62" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B369" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C369" s="62">
         <v>607449</v>
@@ -20197,13 +20196,13 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="62" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B370" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C370" s="62" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="E370" s="72" t="str">
         <f t="shared" si="5"/>
@@ -20212,10 +20211,10 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="62" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B371" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C371" s="62">
         <v>379329</v>
@@ -20227,10 +20226,10 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="62" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B372" s="64" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C372" s="64">
         <v>549405</v>
@@ -20242,10 +20241,10 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" s="62" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B373" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C373" s="62">
         <v>339732</v>
@@ -20257,13 +20256,13 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" s="62" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B374" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C374" s="62" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="E374" s="72" t="str">
         <f t="shared" si="5"/>
@@ -20272,10 +20271,10 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" s="62" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B375" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C375" s="62">
         <v>209673</v>
@@ -20287,10 +20286,10 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" s="62" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B376" s="64" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C376" s="64">
         <v>437373</v>
@@ -20302,10 +20301,10 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" s="62" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B377" s="62" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C377" s="62">
         <v>267716</v>
@@ -20317,13 +20316,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" s="62" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B378" s="62" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C378" s="62" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="E378" s="72" t="str">
         <f t="shared" si="5"/>
@@ -20332,10 +20331,10 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" s="62" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="B379" s="62" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C379" s="62">
         <v>169656</v>
@@ -20347,10 +20346,10 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" s="62" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B380" s="64" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C380" s="64">
         <v>78079</v>
@@ -20362,10 +20361,10 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" s="62" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B381" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C381" s="62">
         <v>72723</v>
@@ -20377,10 +20376,10 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" s="62" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B382" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C382" s="62">
         <v>-6847</v>
@@ -20392,10 +20391,10 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" s="62" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B383" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C383" s="62">
         <v>12204</v>
@@ -20407,10 +20406,10 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" s="62" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B384" s="64" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C384" s="64">
         <v>2231485</v>
@@ -20422,10 +20421,10 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" s="62" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B385" s="62" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C385" s="62">
         <v>1905288</v>
@@ -20437,10 +20436,10 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" s="62" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B386" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C386" s="62">
         <v>-38603</v>
@@ -20452,10 +20451,10 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" s="62" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B387" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C387" s="62">
         <v>364800</v>
@@ -20467,10 +20466,10 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" s="62" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B388" s="64" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C388" s="64">
         <v>2073333</v>
@@ -20482,10 +20481,10 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" s="62" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B389" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C389" s="62">
         <v>1760774</v>
@@ -20497,13 +20496,13 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" s="62" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B390" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C390" s="62" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="E390" s="72" t="str">
         <f t="shared" si="5"/>
@@ -20512,10 +20511,10 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" s="62" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B391" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C391" s="62">
         <v>312559</v>
@@ -20527,10 +20526,10 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392" s="62" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B392" s="64" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C392" s="64">
         <v>158152</v>
@@ -20542,10 +20541,10 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393" s="62" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B393" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C393" s="62">
         <v>144514</v>
@@ -20557,10 +20556,10 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394" s="62" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B394" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C394" s="62">
         <v>-38603</v>
@@ -20572,10 +20571,10 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395" s="62" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B395" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C395" s="62">
         <v>52241</v>
@@ -20587,10 +20586,10 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396" s="62" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B396" s="62" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C396" s="62" t="s">
         <v>9</v>
@@ -20602,10 +20601,10 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397" s="62" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B397" s="64" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C397" s="64">
         <v>4860061</v>
@@ -20617,10 +20616,10 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398" s="62" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B398" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C398" s="62">
         <v>2330991</v>
@@ -20632,10 +20631,10 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A399" s="62" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B399" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C399" s="62">
         <v>189067</v>
@@ -20647,10 +20646,10 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A400" s="62" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B400" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C400" s="62">
         <v>2340002</v>
@@ -20662,10 +20661,10 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A401" s="62" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B401" s="64" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C401" s="64">
         <v>21141611</v>
@@ -20677,10 +20676,10 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A402" s="62" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B402" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C402" s="62">
         <v>10132672</v>
@@ -20692,10 +20691,10 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A403" s="62" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B403" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C403" s="62">
         <v>1716827</v>
@@ -20707,10 +20706,10 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A404" s="62" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B404" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C404" s="62">
         <v>9292113</v>
@@ -20722,10 +20721,10 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A405" s="62" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B405" s="64" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C405" s="64">
         <v>2086166</v>
@@ -20737,10 +20736,10 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A406" s="62" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B406" s="62" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C406" s="62">
         <v>1069020</v>
@@ -20752,10 +20751,10 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A407" s="62" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B407" s="62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C407" s="62">
         <v>76843</v>
@@ -20767,10 +20766,10 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408" s="62" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B408" s="62" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C408" s="62">
         <v>940304</v>
@@ -20782,7 +20781,7 @@
     </row>
     <row r="409" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A409" s="65" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E409" s="72" t="str">
         <f t="shared" si="6"/>
@@ -20791,7 +20790,7 @@
     </row>
     <row r="410" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="66" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="E410" s="72" t="str">
         <f t="shared" si="6"/>
@@ -20800,7 +20799,7 @@
     </row>
     <row r="411" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="66" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="E411" s="72" t="str">
         <f t="shared" si="6"/>
@@ -20809,7 +20808,7 @@
     </row>
     <row r="412" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="66" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="E412" s="72" t="str">
         <f t="shared" si="6"/>
@@ -21031,171 +21030,171 @@
       </c>
       <c r="B2">
         <f>'U.S. Data for ISIC Splits'!L23*10^6*About!$A$36</f>
-        <v>67853809307.303383</v>
+        <v>58613297590.926033</v>
       </c>
       <c r="C2" s="50">
         <f>'U.S. Data for ISIC Splits'!D10*About!$A$36</f>
-        <v>6596078965.0601282</v>
+        <v>5697807437.1825056</v>
       </c>
       <c r="D2" s="56">
         <f>'U.S. Data for ISIC Splits'!L27*10^6*About!$A$36</f>
-        <v>26964606620.659107</v>
+        <v>23292494974.321697</v>
       </c>
       <c r="E2" s="57">
         <f>('U.S. Data for ISIC Splits'!F10-'U.S. Data for ISIC Splits'!D10)*About!$A$36</f>
-        <v>13449442133.216431</v>
+        <v>11617861432.302874</v>
       </c>
       <c r="F2">
         <f>'U.S. Data for ISIC Splits'!L29*10^6*About!$A$36</f>
-        <v>31336695929.438679</v>
+        <v>27069181565.180798</v>
       </c>
       <c r="G2">
         <f>'U.S. Data for ISIC Splits'!L46*10^6*About!$A$36</f>
-        <v>135870301007.49158</v>
+        <v>117367123055.00032</v>
       </c>
       <c r="H2">
         <f>SUM('U.S. Data for ISIC Splits'!L47:L48)*10^6*About!$A$36</f>
-        <v>17268905465.54969</v>
+        <v>14917180117.887459</v>
       </c>
       <c r="I2">
         <f>'U.S. Data for ISIC Splits'!L34*10^6*About!$A$36</f>
-        <v>27365381473.963902</v>
+        <v>23638691245.150448</v>
       </c>
       <c r="J2">
         <f>SUM('U.S. Data for ISIC Splits'!L49:L50)*10^6*About!$A$36</f>
-        <v>53685189651.99099</v>
+        <v>46374198138.921028</v>
       </c>
       <c r="K2" s="19">
         <f>'U.S. Data for ISIC Splits'!T10*About!$A$36</f>
-        <v>18493994109.149982</v>
+        <v>15975432940.767355</v>
       </c>
       <c r="L2" s="50">
         <f>'U.S. Data for ISIC Splits'!G10*About!$A$36</f>
-        <v>77203355475.180481</v>
+        <v>66689597764.376991</v>
       </c>
       <c r="M2" s="50">
         <f>'U.S. Data for ISIC Splits'!H10*About!$A$36</f>
-        <v>38855280373.806473</v>
+        <v>33563865238.788544</v>
       </c>
       <c r="N2">
         <f>'U.S. Data for ISIC Splits'!L53*10^6*About!$A$36</f>
-        <v>52819244831.531158</v>
+        <v>45626179980.809013</v>
       </c>
       <c r="O2" s="50">
         <f>'U.S. Data for ISIC Splits'!J10*About!$A$36</f>
-        <v>6343969172.604372</v>
+        <v>5480030624.9202452</v>
       </c>
       <c r="P2" s="51">
         <f>('U.S. Data for ISIC Splits'!L10-'U.S. Data for ISIC Splits'!$J$10)*About!$A$36</f>
-        <v>26651748242.607639</v>
+        <v>23022242479.970264</v>
       </c>
       <c r="Q2" s="50">
         <f>('U.S. Data for ISIC Splits'!U10+'U.S. Data for ISIC Splits'!M10)*About!$A$36</f>
-        <v>23623483581.0401</v>
+        <v>20406374931.714012</v>
       </c>
       <c r="R2" s="51">
         <f>'U.S. Data for ISIC Splits'!N10*About!$A$36</f>
-        <v>12080330960.21401</v>
+        <v>10435199450.057831</v>
       </c>
       <c r="S2" s="17">
         <f>'U.S. Data for ISIC Splits'!L37*10^6*About!$A$36</f>
-        <v>108538811698.71202</v>
-      </c>
-      <c r="T2" s="83">
+        <v>93757708450.089081</v>
+      </c>
+      <c r="T2">
         <f>'U.S. Data for ISIC Splits'!L39*10^6*About!$A$36</f>
-        <v>158764458589.51172</v>
-      </c>
-      <c r="U2" s="83">
+        <v>137143493536.59195</v>
+      </c>
+      <c r="U2">
         <f>'U.S. Data for ISIC Splits'!L40*10^6*About!$A$36</f>
-        <v>40069012289.183296</v>
-      </c>
-      <c r="V2" s="83">
+        <v>34612307922.815269</v>
+      </c>
+      <c r="V2">
         <f>'U.S. Data for ISIC Splits'!L38*10^6*About!$A$36</f>
-        <v>101686663202.56853</v>
+        <v>87838703709.72522</v>
       </c>
       <c r="W2">
         <f>'U.S. Data for ISIC Splits'!L41*10^6*About!$A$36</f>
-        <v>81843647791.268387</v>
+        <v>70697962765.669174</v>
       </c>
       <c r="X2">
         <f>'U.S. Data for ISIC Splits'!L42*10^6*About!$A$36</f>
-        <v>90090458884.747375</v>
+        <v>77821701251.876846</v>
       </c>
       <c r="Y2" s="17">
         <f>(SUM('U.S. Data for ISIC Splits'!L43:L44)+('U.S. Data for ISIC Splits'!L108*(SUM('U.S. Data for ISIC Splits'!D414)/SUM('U.S. Data for ISIC Splits'!D412:D423))))*10^6*About!$A$36</f>
-        <v>101399919250.7493</v>
+        <v>87591009309.779861</v>
       </c>
       <c r="Z2" s="50">
         <f>'U.S. Data for ISIC Splits'!P10*About!$A$36</f>
-        <v>68515137478.949547</v>
+        <v>59184564338.153259</v>
       </c>
       <c r="AA2" s="50">
         <f>'U.S. Data for ISIC Splits'!Q10*About!$A$36</f>
-        <v>16103497995.245268</v>
+        <v>13910480927.834927</v>
       </c>
       <c r="AB2" s="50">
         <f>('U.S. Data for ISIC Splits'!R10+('U.S. Data for ISIC Splits'!L93*10^6))*About!$A$36</f>
-        <v>44948570113.139557</v>
+        <v>38827354620.523598</v>
       </c>
       <c r="AC2">
         <f>'U.S. Data for ISIC Splits'!L31*10^6*About!$A$36</f>
-        <v>677256969229.0658</v>
+        <v>585026318908.2179</v>
       </c>
       <c r="AD2" s="17">
         <f>(SUM('U.S. Data for ISIC Splits'!L54:L55)+('U.S. Data for ISIC Splits'!L108*(SUM('U.S. Data for ISIC Splits'!D412)/SUM('U.S. Data for ISIC Splits'!D412:D423))))*10^6*About!$A$36</f>
-        <v>1413440692708.2998</v>
+        <v>1220954590384.6421</v>
       </c>
       <c r="AE2">
         <f>SUM('U.S. Data for ISIC Splits'!L61:L68)*10^6*About!$A$36</f>
-        <v>489097835775.17798</v>
+        <v>422491195292.15234</v>
       </c>
       <c r="AF2">
         <f>'U.S. Data for ISIC Splits'!L105*10^6*About!$A$36</f>
-        <v>480345184116.32275</v>
+        <v>414930502950.37433</v>
       </c>
       <c r="AG2" s="17">
         <f>(SUM('U.S. Data for ISIC Splits'!L70:L71)+('U.S. Data for ISIC Splits'!L72*(SUM('U.S. Data for ISIC Splits'!D337:D338)/SUM('U.S. Data for ISIC Splits'!D337:D341))))*10^6*About!$A$36</f>
-        <v>219311592512.91263</v>
+        <v>189445158176.48669</v>
       </c>
       <c r="AH2" s="17">
         <f>('U.S. Data for ISIC Splits'!L72*(SUM('U.S. Data for ISIC Splits'!D339:D341)/SUM('U.S. Data for ISIC Splits'!D337:D341)))*10^6*About!$A$36</f>
-        <v>82872646878.901917</v>
+        <v>71586830028.391342</v>
       </c>
       <c r="AI2">
         <f>('U.S. Data for ISIC Splits'!L88+'U.S. Data for ISIC Splits'!L73)*10^6*About!$A$36</f>
-        <v>577599599416.90955</v>
+        <v>498940554032.81586</v>
       </c>
       <c r="AJ2">
         <f>'U.S. Data for ISIC Splits'!L75*10^6*About!$A$36</f>
-        <v>945059301649.62891</v>
+        <v>816358619422.42139</v>
       </c>
       <c r="AK2">
         <f>'U.S. Data for ISIC Splits'!L80*10^6*About!$A$36</f>
-        <v>189441104601.98541</v>
+        <v>163642512533.11398</v>
       </c>
       <c r="AL2">
         <f>SUM('U.S. Data for ISIC Splits'!L87,'U.S. Data for ISIC Splits'!L89:L90,'U.S. Data for ISIC Splits'!L92)*10^6*About!$A$36</f>
-        <v>1891109101826.7703</v>
+        <v>1633572848655.834</v>
       </c>
       <c r="AM2">
         <f>'U.S. Data for ISIC Splits'!L109*10^6*About!$A$36</f>
-        <v>2190670087633.3169</v>
+        <v>1892338824906.1965</v>
       </c>
       <c r="AN2">
         <f>'U.S. Data for ISIC Splits'!L95*10^6*About!$A$36</f>
-        <v>227079201343.32211</v>
+        <v>196154953434.77136</v>
       </c>
       <c r="AO2">
         <f>'U.S. Data for ISIC Splits'!L96*10^6*About!$A$36</f>
-        <v>1500946732745.322</v>
+        <v>1296543825801.9883</v>
       </c>
       <c r="AP2">
         <f>('U.S. Data for ISIC Splits'!L102+('U.S. Data for ISIC Splits'!L108*(SUM('U.S. Data for ISIC Splits'!D413,'U.S. Data for ISIC Splits'!D415:D422)/SUM('U.S. Data for ISIC Splits'!D412:D423))))*10^6*About!$A$36</f>
-        <v>409261095970.61041</v>
-      </c>
-      <c r="AQ2" s="84">
+        <v>353526834460.74396</v>
+      </c>
+      <c r="AQ2" s="73">
         <f>('U.S. Data for ISIC Splits'!L108*('U.S. Data for ISIC Splits'!D423/SUM('U.S. Data for ISIC Splits'!D412:D423)))*10^6*About!$A$36</f>
-        <v>9269229273.720705</v>
+        <v>8006921046.9608421</v>
       </c>
     </row>
   </sheetData>
